--- a/V05.xlsx
+++ b/V05.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="20730" windowHeight="11760" firstSheet="8" activeTab="11"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="20730" windowHeight="11760" firstSheet="8" activeTab="16"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -23,6 +23,7 @@
     <sheet name="APP STORE (2)" sheetId="15" r:id="rId14"/>
     <sheet name="APP STORE (3)" sheetId="17" r:id="rId15"/>
     <sheet name="APPLE GER" sheetId="18" r:id="rId16"/>
+    <sheet name="Roblox " sheetId="20" r:id="rId17"/>
   </sheets>
   <calcPr calcId="124519"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1360" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1373" uniqueCount="439">
   <si>
     <t>Name</t>
   </si>
@@ -1450,6 +1451,27 @@
   </si>
   <si>
     <t>G</t>
+  </si>
+  <si>
+    <t>800 Robux</t>
+  </si>
+  <si>
+    <t>lotkeys</t>
+  </si>
+  <si>
+    <t>2000 Robux</t>
+  </si>
+  <si>
+    <t>4500 Robux</t>
+  </si>
+  <si>
+    <t>10000 Robux</t>
+  </si>
+  <si>
+    <t>USDTCOST</t>
+  </si>
+  <si>
+    <t>RATE</t>
   </si>
 </sst>
 </file>
@@ -1629,7 +1651,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1728,6 +1750,13 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -9072,7 +9101,7 @@
       </c>
     </row>
     <row r="2" spans="1:13" ht="21" customHeight="1" thickBot="1">
-      <c r="B2" s="36">
+      <c r="B2" s="39">
         <v>3</v>
       </c>
       <c r="H2" s="11"/>
@@ -9081,7 +9110,7 @@
       <c r="K2" s="21"/>
     </row>
     <row r="3" spans="1:13" ht="21" customHeight="1" thickBot="1">
-      <c r="B3" s="36"/>
+      <c r="B3" s="39"/>
       <c r="H3" s="11"/>
       <c r="I3" s="18"/>
       <c r="J3" s="21"/>
@@ -9560,7 +9589,7 @@
       </c>
     </row>
     <row r="20" spans="1:12" ht="21" customHeight="1" thickBot="1">
-      <c r="B20" s="36">
+      <c r="B20" s="39">
         <v>2</v>
       </c>
       <c r="H20" s="11"/>
@@ -9569,7 +9598,7 @@
       <c r="K20" s="21"/>
     </row>
     <row r="21" spans="1:12" ht="21" customHeight="1" thickBot="1">
-      <c r="B21" s="36"/>
+      <c r="B21" s="39"/>
       <c r="H21" s="11"/>
       <c r="I21" s="18"/>
       <c r="J21" s="21"/>
@@ -10007,7 +10036,7 @@
       <c r="N36" s="2"/>
     </row>
     <row r="37" spans="1:14" ht="21" customHeight="1" thickBot="1">
-      <c r="B37" s="36">
+      <c r="B37" s="39">
         <v>1</v>
       </c>
       <c r="I37" s="6"/>
@@ -10016,7 +10045,7 @@
       <c r="N37" s="2"/>
     </row>
     <row r="38" spans="1:14" ht="21" customHeight="1" thickBot="1">
-      <c r="B38" s="36"/>
+      <c r="B38" s="39"/>
       <c r="I38" s="6"/>
       <c r="J38" s="8"/>
       <c r="K38" s="8"/>
@@ -10549,14 +10578,14 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="21" customHeight="1" thickBot="1">
-      <c r="B2" s="36"/>
+      <c r="B2" s="39"/>
       <c r="G2" s="11"/>
       <c r="H2" s="18"/>
       <c r="I2" s="21"/>
       <c r="J2" s="21"/>
     </row>
     <row r="3" spans="1:11" ht="21" customHeight="1" thickBot="1">
-      <c r="B3" s="36"/>
+      <c r="B3" s="39"/>
       <c r="G3" s="11"/>
       <c r="H3" s="18"/>
       <c r="I3" s="21"/>
@@ -11000,14 +11029,14 @@
       <c r="J19" s="1"/>
     </row>
     <row r="20" spans="1:10" ht="21" customHeight="1" thickBot="1">
-      <c r="B20" s="36"/>
+      <c r="B20" s="39"/>
       <c r="G20" s="11"/>
       <c r="H20" s="18"/>
       <c r="I20" s="21"/>
       <c r="J20" s="21"/>
     </row>
     <row r="21" spans="1:10" ht="21" customHeight="1" thickBot="1">
-      <c r="B21" s="36"/>
+      <c r="B21" s="39"/>
       <c r="G21" s="11"/>
       <c r="H21" s="18"/>
       <c r="I21" s="21"/>
@@ -11109,14 +11138,14 @@
       <c r="M36" s="2"/>
     </row>
     <row r="37" spans="1:13" ht="21" customHeight="1" thickBot="1">
-      <c r="B37" s="36"/>
+      <c r="B37" s="39"/>
       <c r="H37" s="6"/>
       <c r="I37" s="8"/>
       <c r="J37" s="8"/>
       <c r="M37" s="2"/>
     </row>
     <row r="38" spans="1:13" ht="21" customHeight="1" thickBot="1">
-      <c r="B38" s="36"/>
+      <c r="B38" s="39"/>
       <c r="H38" s="6"/>
       <c r="I38" s="8"/>
       <c r="J38" s="8"/>
@@ -11406,7 +11435,7 @@
       <c r="M1" s="28"/>
     </row>
     <row r="2" spans="1:13" ht="21" customHeight="1">
-      <c r="B2" s="37">
+      <c r="B2" s="40">
         <v>1</v>
       </c>
       <c r="G2" s="30"/>
@@ -11415,7 +11444,7 @@
       <c r="J2" s="31"/>
     </row>
     <row r="3" spans="1:13" ht="21" customHeight="1">
-      <c r="B3" s="37"/>
+      <c r="B3" s="40"/>
       <c r="G3" s="30"/>
       <c r="H3" s="31"/>
       <c r="I3" s="31"/>
@@ -11640,7 +11669,7 @@
       <c r="J14" s="31"/>
     </row>
     <row r="15" spans="1:13" ht="21" customHeight="1">
-      <c r="B15" s="37">
+      <c r="B15" s="40">
         <v>2</v>
       </c>
       <c r="G15" s="30"/>
@@ -11649,7 +11678,7 @@
       <c r="J15" s="31"/>
     </row>
     <row r="16" spans="1:13" ht="21" customHeight="1">
-      <c r="B16" s="37"/>
+      <c r="B16" s="40"/>
       <c r="G16" s="30"/>
       <c r="H16" s="31"/>
       <c r="I16" s="31"/>
@@ -11992,14 +12021,14 @@
       <c r="M35" s="28"/>
     </row>
     <row r="36" spans="2:13" ht="21" customHeight="1">
-      <c r="B36" s="37"/>
+      <c r="B36" s="40"/>
       <c r="H36" s="34"/>
       <c r="I36" s="34"/>
       <c r="J36" s="34"/>
       <c r="M36" s="28"/>
     </row>
     <row r="37" spans="2:13" ht="21" customHeight="1">
-      <c r="B37" s="37"/>
+      <c r="B37" s="40"/>
       <c r="H37" s="34"/>
       <c r="I37" s="34"/>
       <c r="J37" s="34"/>
@@ -12222,6 +12251,231 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:O16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="18.75"/>
+  <cols>
+    <col min="1" max="1" width="11.5703125" style="36"/>
+    <col min="2" max="2" width="16.7109375" style="36" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" style="36" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.5703125" style="36" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.85546875" style="36" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="36" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="36" customWidth="1"/>
+    <col min="8" max="8" width="12.5703125" style="36" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="11.5703125" style="36"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:15" s="28" customFormat="1" ht="21" customHeight="1">
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38"/>
+    </row>
+    <row r="3" spans="1:15" s="19" customFormat="1">
+      <c r="B3" s="19" t="s">
+        <v>343</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>437</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>438</v>
+      </c>
+      <c r="E3" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="29" t="s">
+        <v>429</v>
+      </c>
+      <c r="G3" s="29" t="s">
+        <v>430</v>
+      </c>
+      <c r="H3" s="19" t="s">
+        <v>311</v>
+      </c>
+      <c r="I3" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="J3" s="19" t="s">
+        <v>340</v>
+      </c>
+      <c r="N3" s="20"/>
+      <c r="O3" s="20"/>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" s="19"/>
+      <c r="B4" s="19" t="s">
+        <v>432</v>
+      </c>
+      <c r="C4" s="20">
+        <f>J4+0.5</f>
+        <v>10.68</v>
+      </c>
+      <c r="D4" s="19">
+        <v>43</v>
+      </c>
+      <c r="E4" s="20">
+        <f>C4*D4</f>
+        <v>459.24</v>
+      </c>
+      <c r="F4" s="36">
+        <f>E4*0.12</f>
+        <v>55.108800000000002</v>
+      </c>
+      <c r="G4" s="20">
+        <f>E4+F4</f>
+        <v>514.34879999999998</v>
+      </c>
+      <c r="H4" s="19">
+        <v>10.029999999999999</v>
+      </c>
+      <c r="I4" s="19">
+        <v>10.02</v>
+      </c>
+      <c r="J4" s="19">
+        <v>10.18</v>
+      </c>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="19"/>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" s="19"/>
+      <c r="B5" s="37" t="s">
+        <v>434</v>
+      </c>
+      <c r="C5" s="20">
+        <f>J5+0.5</f>
+        <v>25.95</v>
+      </c>
+      <c r="D5" s="19">
+        <v>43</v>
+      </c>
+      <c r="E5" s="20">
+        <f t="shared" ref="E5:E7" si="0">C5*D5</f>
+        <v>1115.8499999999999</v>
+      </c>
+      <c r="F5" s="36">
+        <f t="shared" ref="F5:F7" si="1">E5*0.12</f>
+        <v>133.90199999999999</v>
+      </c>
+      <c r="G5" s="20">
+        <f t="shared" ref="G5:G7" si="2">E5+F5</f>
+        <v>1249.752</v>
+      </c>
+      <c r="H5" s="19">
+        <v>25.37</v>
+      </c>
+      <c r="I5" s="19">
+        <v>25.07</v>
+      </c>
+      <c r="J5" s="19">
+        <v>25.45</v>
+      </c>
+      <c r="K5" s="19"/>
+      <c r="L5" s="19"/>
+      <c r="M5" s="19"/>
+      <c r="N5" s="19"/>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" s="19"/>
+      <c r="B6" s="37" t="s">
+        <v>435</v>
+      </c>
+      <c r="C6" s="20">
+        <f>J6+0.5</f>
+        <v>51.35</v>
+      </c>
+      <c r="D6" s="19">
+        <v>43</v>
+      </c>
+      <c r="E6" s="20">
+        <f t="shared" si="0"/>
+        <v>2208.0500000000002</v>
+      </c>
+      <c r="F6" s="36">
+        <f t="shared" si="1"/>
+        <v>264.96600000000001</v>
+      </c>
+      <c r="G6" s="20">
+        <f t="shared" si="2"/>
+        <v>2473.0160000000001</v>
+      </c>
+      <c r="H6" s="19">
+        <v>49.63</v>
+      </c>
+      <c r="I6" s="19">
+        <v>50.15</v>
+      </c>
+      <c r="J6" s="19">
+        <v>50.85</v>
+      </c>
+      <c r="K6" s="19"/>
+      <c r="L6" s="19"/>
+      <c r="M6" s="19"/>
+      <c r="N6" s="19"/>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" s="19"/>
+      <c r="B7" s="37" t="s">
+        <v>436</v>
+      </c>
+      <c r="C7" s="20">
+        <f>J7+0.5</f>
+        <v>101.78</v>
+      </c>
+      <c r="D7" s="19">
+        <v>43</v>
+      </c>
+      <c r="E7" s="20">
+        <f t="shared" si="0"/>
+        <v>4376.54</v>
+      </c>
+      <c r="F7" s="36">
+        <f t="shared" si="1"/>
+        <v>525.1848</v>
+      </c>
+      <c r="G7" s="20">
+        <f t="shared" si="2"/>
+        <v>4901.7248</v>
+      </c>
+      <c r="H7" s="19">
+        <v>99.62</v>
+      </c>
+      <c r="I7" s="19">
+        <v>100.31</v>
+      </c>
+      <c r="J7" s="19">
+        <v>101.28</v>
+      </c>
+      <c r="K7" s="19"/>
+      <c r="L7" s="19"/>
+      <c r="M7" s="19"/>
+      <c r="N7" s="19"/>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="B15" s="19"/>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="B16" s="19"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="51" fitToHeight="0" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
